--- a/artfynd/A 2554-2024 artfynd.xlsx
+++ b/artfynd/A 2554-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2554-2024 artfynd.xlsx
+++ b/artfynd/A 2554-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -910,126 +910,6 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>114461523</v>
-      </c>
-      <c r="B4" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Sinäs, Upl</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>602915</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6654702</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Heby</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Enåker</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>C-Heb-0275</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2017-10-09</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2017-10-09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>3 blommande  och flera vegetativa</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Ingvar Sundh</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Niina Sallmén</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2554-2024 artfynd.xlsx
+++ b/artfynd/A 2554-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>69681365</v>
       </c>
       <c r="B2" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602969.8091264309</v>
+        <v>602970</v>
       </c>
       <c r="R2" t="n">
-        <v>6654726.977869513</v>
+        <v>6654727</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>2017-10-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-10-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,12 +779,7 @@
         <v>69681315</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -835,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602914.8622574764</v>
+        <v>602915</v>
       </c>
       <c r="R3" t="n">
-        <v>6654702.933277783</v>
+        <v>6654703</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,19 +848,9 @@
           <t>2017-10-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-10-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -909,6 +879,121 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>114461523</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sinäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>602915</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6654702</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Enåker</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>C-Heb-0275</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2017-10-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2017-10-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>3 blommande  och flera vegetativa</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ingvar Sundh</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2554-2024 artfynd.xlsx
+++ b/artfynd/A 2554-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69681365</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69681315</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,8 +1009,18 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114461523</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>